--- a/aplicacion/plantillas/PlantilaPagoExcel.xlsx
+++ b/aplicacion/plantillas/PlantilaPagoExcel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patricio Leon\OneDrive\Documentos\GitHub\EmpresaElectrica\aplicacion\plantillas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patricio Leon\Documents\Github\EmpresaElectrica\aplicacion\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D40A08B-C117-498F-940D-B848CA7CB23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BA9219-D6C8-46A5-84CC-33A27B97EBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Estado!$A$1:$G$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Ppago!$A$1:$G$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Ppago!$A$1:$G$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1184,66 +1184,69 @@
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="8"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="8"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="8"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="8"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1261,9 +1264,6 @@
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1735,7 +1735,7 @@
   <sheetPr codeName="Hoja6">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5546875" style="1" customWidth="1"/>
@@ -1755,22 +1755,22 @@
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
     </row>
     <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="A8" s="122" t="s">
+      <c r="A8" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="122"/>
-      <c r="C8" s="122"/>
-      <c r="D8" s="122"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="122"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="111"/>
+      <c r="G8" s="111"/>
       <c r="H8" s="3"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1801,7 +1801,7 @@
       <c r="F13" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="135"/>
+      <c r="G13" s="109"/>
     </row>
     <row r="14" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
@@ -1815,7 +1815,7 @@
       <c r="F14" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="135"/>
+      <c r="G14" s="109"/>
       <c r="K14" s="13"/>
       <c r="L14" s="14"/>
     </row>
@@ -1827,11 +1827,11 @@
       <c r="D15" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="123" t="s">
+      <c r="E15" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="124"/>
-      <c r="G15" s="124"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="113"/>
     </row>
     <row r="16" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
@@ -1885,10 +1885,10 @@
       <c r="A20" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="125" t="s">
+      <c r="B20" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="126"/>
+      <c r="C20" s="115"/>
       <c r="D20" s="25" t="s">
         <v>22</v>
       </c>
@@ -1904,8 +1904,8 @@
     </row>
     <row r="21" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="28"/>
-      <c r="B21" s="127"/>
-      <c r="C21" s="128"/>
+      <c r="B21" s="116"/>
+      <c r="C21" s="117"/>
       <c r="D21" s="29"/>
       <c r="E21" s="30"/>
       <c r="F21" s="31"/>
@@ -1983,7 +1983,7 @@
       <c r="G28" s="32"/>
       <c r="I28" s="33"/>
     </row>
-    <row r="29" spans="1:11" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="28"/>
       <c r="B29" s="35"/>
       <c r="C29" s="36"/>
@@ -1991,291 +1991,297 @@
       <c r="E29" s="38"/>
       <c r="F29" s="31"/>
       <c r="G29" s="32"/>
-    </row>
-    <row r="30" spans="1:11" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="I29" s="33"/>
+    </row>
+    <row r="30" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="28"/>
       <c r="B30" s="35"/>
-      <c r="C30" s="39"/>
+      <c r="C30" s="36"/>
       <c r="D30" s="37"/>
       <c r="E30" s="38"/>
       <c r="F30" s="31"/>
       <c r="G30" s="32"/>
+      <c r="I30" s="33"/>
     </row>
     <row r="31" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="28"/>
-      <c r="B31" s="40" t="s">
+      <c r="B31" s="35"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="32"/>
+      <c r="I31" s="33"/>
+    </row>
+    <row r="32" spans="1:11" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A32" s="28"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="32"/>
+    </row>
+    <row r="33" spans="1:8" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A33" s="28"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="32"/>
+    </row>
+    <row r="34" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="28"/>
+      <c r="B34" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="43"/>
-    </row>
-    <row r="32" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
-      <c r="B32" s="40"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="45"/>
-    </row>
-    <row r="33" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="28"/>
-      <c r="B33" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="43"/>
-    </row>
-    <row r="34" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="28"/>
-      <c r="B34" s="112" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="112"/>
-      <c r="D34" s="112"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="41"/>
       <c r="E34" s="42"/>
       <c r="F34" s="42"/>
       <c r="G34" s="43"/>
     </row>
-    <row r="35" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="28"/>
-      <c r="B35" s="120" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="120"/>
-      <c r="D35" s="120"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="44"/>
       <c r="E35" s="42"/>
       <c r="F35" s="42"/>
-      <c r="G35" s="46"/>
-    </row>
-    <row r="36" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="G35" s="43"/>
+      <c r="H35" s="45"/>
+    </row>
+    <row r="36" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="28"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="49"/>
+      <c r="B36" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="17"/>
+      <c r="D36" s="44"/>
       <c r="E36" s="42"/>
       <c r="F36" s="42"/>
       <c r="G36" s="43"/>
     </row>
-    <row r="37" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="28"/>
-      <c r="B37" s="120" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="120"/>
-      <c r="D37" s="120"/>
+      <c r="B37" s="118" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="118"/>
+      <c r="D37" s="118"/>
       <c r="E37" s="42"/>
       <c r="F37" s="42"/>
       <c r="G37" s="43"/>
     </row>
-    <row r="38" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="28"/>
-      <c r="B38" s="118" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="118"/>
-      <c r="D38" s="118"/>
+      <c r="B38" s="119" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="119"/>
+      <c r="D38" s="119"/>
       <c r="E38" s="42"/>
       <c r="F38" s="42"/>
-      <c r="G38" s="43"/>
-    </row>
-    <row r="39" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="G38" s="46"/>
+    </row>
+    <row r="39" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="28"/>
-      <c r="B39" s="118" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="118"/>
-      <c r="D39" s="118"/>
+      <c r="B39" s="47"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="49"/>
       <c r="E39" s="42"/>
       <c r="F39" s="42"/>
       <c r="G39" s="43"/>
     </row>
-    <row r="40" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="28"/>
-      <c r="B40" s="118" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="118"/>
-      <c r="D40" s="118"/>
+      <c r="B40" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="119"/>
+      <c r="D40" s="119"/>
       <c r="E40" s="42"/>
       <c r="F40" s="42"/>
       <c r="G40" s="43"/>
     </row>
-    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="28"/>
-      <c r="B41" s="119" t="s">
-        <v>33</v>
-      </c>
-      <c r="C41" s="119"/>
-      <c r="D41" s="119"/>
+      <c r="B41" s="120" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="120"/>
+      <c r="D41" s="120"/>
       <c r="E41" s="42"/>
       <c r="F41" s="42"/>
       <c r="G41" s="43"/>
     </row>
-    <row r="42" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="28"/>
-      <c r="B42" s="119"/>
-      <c r="C42" s="119"/>
-      <c r="D42" s="119"/>
+      <c r="B42" s="120" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="120"/>
+      <c r="D42" s="120"/>
       <c r="E42" s="42"/>
       <c r="F42" s="42"/>
       <c r="G42" s="43"/>
     </row>
-    <row r="43" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="28"/>
       <c r="B43" s="120" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C43" s="120"/>
       <c r="D43" s="120"/>
       <c r="E43" s="42"/>
       <c r="F43" s="42"/>
-      <c r="G43" s="46"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G43" s="43"/>
+    </row>
+    <row r="44" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="28"/>
-      <c r="B44" s="112"/>
-      <c r="C44" s="112"/>
-      <c r="D44" s="112"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="32"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="121" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="121"/>
+      <c r="D44" s="121"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="43"/>
+    </row>
+    <row r="45" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="28"/>
-      <c r="B45" s="112"/>
-      <c r="C45" s="112"/>
-      <c r="D45" s="112"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="32"/>
-    </row>
-    <row r="46" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="50"/>
-      <c r="B46" s="113"/>
-      <c r="C46" s="113"/>
-      <c r="D46" s="113"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="51"/>
-      <c r="G46" s="52"/>
-    </row>
-    <row r="47" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E47" s="53" t="s">
+      <c r="B45" s="121"/>
+      <c r="C45" s="121"/>
+      <c r="D45" s="121"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="43"/>
+    </row>
+    <row r="46" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A46" s="28"/>
+      <c r="B46" s="119" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" s="119"/>
+      <c r="D46" s="119"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="46"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="28"/>
+      <c r="B47" s="118"/>
+      <c r="C47" s="118"/>
+      <c r="D47" s="118"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="32"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="28"/>
+      <c r="B48" s="118"/>
+      <c r="C48" s="118"/>
+      <c r="D48" s="118"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="32"/>
+    </row>
+    <row r="49" spans="1:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="50"/>
+      <c r="B49" s="128"/>
+      <c r="C49" s="128"/>
+      <c r="D49" s="128"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="51"/>
+      <c r="G49" s="52"/>
+    </row>
+    <row r="50" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E50" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="F47" s="54"/>
-      <c r="G47" s="55"/>
-    </row>
-    <row r="50" spans="2:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="114"/>
-      <c r="C50" s="114"/>
-      <c r="D50" s="114"/>
-      <c r="E50" s="114"/>
-      <c r="F50" s="114"/>
-      <c r="G50" s="114"/>
-    </row>
-    <row r="53" spans="2:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="115"/>
-      <c r="C53" s="115"/>
-      <c r="D53" s="115"/>
-      <c r="E53" s="115"/>
-      <c r="F53" s="115"/>
-      <c r="G53" s="115"/>
-    </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B57" s="56"/>
-      <c r="C57" s="56"/>
-      <c r="D57" s="56"/>
-      <c r="E57" s="56"/>
-      <c r="F57" s="56"/>
-      <c r="G57" s="56"/>
-    </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B58" s="56"/>
-      <c r="C58" s="56"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="56"/>
-      <c r="G58" s="56"/>
-    </row>
-    <row r="59" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="116" t="s">
+      <c r="F50" s="54"/>
+      <c r="G50" s="55"/>
+    </row>
+    <row r="53" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="129"/>
+      <c r="C53" s="129"/>
+      <c r="D53" s="129"/>
+      <c r="E53" s="129"/>
+      <c r="F53" s="129"/>
+      <c r="G53" s="129"/>
+    </row>
+    <row r="56" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="123"/>
+      <c r="C56" s="123"/>
+      <c r="D56" s="123"/>
+      <c r="E56" s="123"/>
+      <c r="F56" s="123"/>
+      <c r="G56" s="123"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B60" s="56"/>
+      <c r="C60" s="56"/>
+      <c r="D60" s="56"/>
+      <c r="E60" s="56"/>
+      <c r="F60" s="56"/>
+      <c r="G60" s="56"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B61" s="56"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="56"/>
+      <c r="E61" s="56"/>
+      <c r="F61" s="56"/>
+      <c r="G61" s="56"/>
+    </row>
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="124" t="s">
         <v>41</v>
       </c>
-      <c r="C59" s="116"/>
-      <c r="D59" s="56"/>
-      <c r="E59" s="117" t="s">
+      <c r="C62" s="124"/>
+      <c r="D62" s="56"/>
+      <c r="E62" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="F59" s="117"/>
-      <c r="G59" s="56"/>
-    </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B60" s="56" t="s">
+      <c r="F62" s="125"/>
+      <c r="G62" s="56"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B63" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="57"/>
-      <c r="D60" s="56"/>
-      <c r="E60" s="117" t="s">
+      <c r="C63" s="57"/>
+      <c r="D63" s="56"/>
+      <c r="E63" s="125" t="s">
         <v>38</v>
       </c>
-      <c r="F60" s="117"/>
-      <c r="G60" s="56"/>
-      <c r="K60" s="109"/>
-      <c r="L60" s="109"/>
-    </row>
-    <row r="61" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="110" t="s">
+      <c r="F63" s="125"/>
+      <c r="G63" s="56"/>
+      <c r="K63" s="126"/>
+      <c r="L63" s="126"/>
+    </row>
+    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="C61" s="110"/>
-      <c r="D61" s="110"/>
-      <c r="E61" s="110" t="s">
+      <c r="C64" s="122"/>
+      <c r="D64" s="122"/>
+      <c r="E64" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="F61" s="110"/>
-      <c r="G61" s="110"/>
-      <c r="K61" s="111"/>
-      <c r="L61" s="111"/>
-    </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B62" s="56"/>
-      <c r="C62" s="56"/>
-      <c r="D62" s="56"/>
-      <c r="E62" s="110"/>
-      <c r="F62" s="110"/>
-      <c r="G62" s="110"/>
-    </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B63" s="56"/>
-      <c r="C63" s="56"/>
-      <c r="D63" s="56"/>
-      <c r="E63" s="56"/>
-      <c r="F63" s="56"/>
-      <c r="G63" s="56"/>
-    </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B64" s="58"/>
-      <c r="C64" s="58"/>
-      <c r="D64" s="56"/>
-      <c r="E64" s="56"/>
-      <c r="F64" s="56"/>
-      <c r="G64" s="56"/>
+      <c r="F64" s="122"/>
+      <c r="G64" s="122"/>
+      <c r="K64" s="127"/>
+      <c r="L64" s="127"/>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B65" s="56"/>
       <c r="C65" s="56"/>
       <c r="D65" s="56"/>
-      <c r="E65" s="56"/>
-      <c r="F65" s="56"/>
-      <c r="G65" s="56"/>
+      <c r="E65" s="122"/>
+      <c r="F65" s="122"/>
+      <c r="G65" s="122"/>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B66" s="56"/>
@@ -2286,42 +2292,66 @@
       <c r="G66" s="56"/>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B67" s="56"/>
-      <c r="C67" s="56"/>
+      <c r="B67" s="58"/>
+      <c r="C67" s="58"/>
       <c r="D67" s="56"/>
       <c r="E67" s="56"/>
       <c r="F67" s="56"/>
       <c r="G67" s="56"/>
     </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="56"/>
+      <c r="C68" s="56"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="56"/>
+      <c r="F68" s="56"/>
+      <c r="G68" s="56"/>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B69" s="56"/>
+      <c r="C69" s="56"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="56"/>
+      <c r="F69" s="56"/>
+      <c r="G69" s="56"/>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B70" s="56"/>
+      <c r="C70" s="56"/>
+      <c r="D70" s="56"/>
+      <c r="E70" s="56"/>
+      <c r="F70" s="56"/>
+      <c r="G70" s="56"/>
+    </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B50:G50"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.78740157480314965" right="0.47244094488188981" top="0.98425196850393704" bottom="0.59055118110236227" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -2354,30 +2384,30 @@
       <c r="B1" s="2"/>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
     </row>
     <row r="8" spans="2:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="B8" s="122" t="s">
+      <c r="B8" s="111" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="122"/>
-      <c r="D8" s="122"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="122"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="111"/>
+      <c r="G8" s="111"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="129" t="s">
+      <c r="B10" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="129"/>
+      <c r="C10" s="130"/>
+      <c r="D10" s="130"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="130"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F12" s="1" t="s">
@@ -2440,14 +2470,14 @@
     </row>
     <row r="22" spans="2:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="2:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="130" t="s">
+      <c r="B23" s="131" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="130"/>
-      <c r="D23" s="130"/>
-      <c r="E23" s="130"/>
-      <c r="F23" s="130"/>
-      <c r="G23" s="130"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="131"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="131"/>
+      <c r="G23" s="131"/>
     </row>
     <row r="24" spans="2:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B24" s="70" t="s">
@@ -2580,14 +2610,14 @@
       <c r="G41" s="69"/>
     </row>
     <row r="42" spans="2:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="131" t="s">
+      <c r="B42" s="132" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="131"/>
-      <c r="D42" s="131"/>
-      <c r="E42" s="131"/>
-      <c r="F42" s="131"/>
-      <c r="G42" s="131"/>
+      <c r="C42" s="132"/>
+      <c r="D42" s="132"/>
+      <c r="E42" s="132"/>
+      <c r="F42" s="132"/>
+      <c r="G42" s="132"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43" s="93" t="s">
@@ -2635,58 +2665,58 @@
       <c r="G48" s="101"/>
     </row>
     <row r="54" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="109" t="str">
+      <c r="B54" s="126" t="str">
         <f>[1]Ppago!B59</f>
         <v>RAFAEL ORELLANA CALDERÓN</v>
       </c>
-      <c r="C54" s="109"/>
-      <c r="E54" s="109" t="s">
+      <c r="C54" s="126"/>
+      <c r="E54" s="126" t="s">
         <v>40</v>
       </c>
-      <c r="F54" s="109"/>
+      <c r="F54" s="126"/>
     </row>
     <row r="55" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="109" t="str">
+      <c r="B55" s="126" t="str">
         <f>[1]Ppago!E60</f>
         <v>DARWIN PATRICIO LEÓN BRABO</v>
       </c>
-      <c r="C55" s="109"/>
-      <c r="D55" s="109"/>
-      <c r="E55" s="109"/>
-      <c r="F55" s="109"/>
-      <c r="G55" s="109"/>
+      <c r="C55" s="126"/>
+      <c r="D55" s="126"/>
+      <c r="E55" s="126"/>
+      <c r="F55" s="126"/>
+      <c r="G55" s="126"/>
     </row>
     <row r="56" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="111" t="s">
+      <c r="B56" s="127" t="s">
         <v>48</v>
       </c>
-      <c r="C56" s="111"/>
-      <c r="D56" s="111"/>
-      <c r="E56" s="111"/>
-      <c r="F56" s="111"/>
-      <c r="G56" s="111"/>
+      <c r="C56" s="127"/>
+      <c r="D56" s="127"/>
+      <c r="E56" s="127"/>
+      <c r="F56" s="127"/>
+      <c r="G56" s="127"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E59" s="109"/>
-      <c r="F59" s="109"/>
+      <c r="E59" s="126"/>
+      <c r="F59" s="126"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
+      <c r="E60" s="127"/>
+      <c r="F60" s="127"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B42:G42"/>
     <mergeCell ref="E60:F60"/>
     <mergeCell ref="B54:C54"/>
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="E59:F59"/>
     <mergeCell ref="B55:G55"/>
     <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B42:G42"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.74803149606299213" top="0.78740157480314965" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -2709,34 +2739,34 @@
   </cols>
   <sheetData>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="132"/>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
+      <c r="A8" s="133"/>
+      <c r="B8" s="133"/>
+      <c r="C8" s="133"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="133"/>
     </row>
     <row r="9" spans="1:5" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="132"/>
-      <c r="B9" s="132"/>
-      <c r="C9" s="132"/>
-      <c r="D9" s="132"/>
-      <c r="E9" s="132"/>
+      <c r="A9" s="133"/>
+      <c r="B9" s="133"/>
+      <c r="C9" s="133"/>
+      <c r="D9" s="133"/>
+      <c r="E9" s="133"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="133" t="s">
+      <c r="A10" s="134" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="133"/>
-      <c r="C10" s="133"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="133"/>
+      <c r="B10" s="134"/>
+      <c r="C10" s="134"/>
+      <c r="D10" s="134"/>
+      <c r="E10" s="134"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="133"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="133"/>
-      <c r="E11" s="133"/>
+      <c r="A11" s="134"/>
+      <c r="B11" s="134"/>
+      <c r="C11" s="134"/>
+      <c r="D11" s="134"/>
+      <c r="E11" s="134"/>
     </row>
     <row r="12" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.3">
@@ -2786,11 +2816,11 @@
       <c r="B29" s="17"/>
     </row>
     <row r="30" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="134" t="s">
+      <c r="A30" s="135" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="134"/>
-      <c r="C30" s="134"/>
+      <c r="B30" s="135"/>
+      <c r="C30" s="135"/>
     </row>
   </sheetData>
   <mergeCells count="3">
